--- a/templates/contribution_template.xlsx
+++ b/templates/contribution_template.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Tristan/Documents/GitHub-repos/401-k-Modeller/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E237007-352D-094E-8876-7C929F7372C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DFE79-28C8-F44B-9DAD-5ECEB1199683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
     <sheet name="Contributions" sheetId="2" r:id="rId2"/>
-    <sheet name="Tax Brackets" sheetId="3" r:id="rId3"/>
-    <sheet name="IRS Limits" sheetId="4" r:id="rId4"/>
-    <sheet name="Conversions" sheetId="5" r:id="rId5"/>
+    <sheet name="Withdrawals" sheetId="6" r:id="rId3"/>
+    <sheet name="Tax Brackets" sheetId="3" r:id="rId4"/>
+    <sheet name="IRS Limits" sheetId="4" r:id="rId5"/>
+    <sheet name="Conversions" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="32">
   <si>
     <t>Field</t>
   </si>
@@ -146,6 +147,15 @@
   </si>
   <si>
     <t>Starting Year</t>
+  </si>
+  <si>
+    <t>End Age</t>
+  </si>
+  <si>
+    <t>Withdrawl ($)</t>
+  </si>
+  <si>
+    <t>Traditional Bracket Limit (%)</t>
   </si>
 </sst>
 </file>
@@ -499,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -540,57 +550,65 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>10000</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>65000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>2.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>0</v>
       </c>
     </row>
@@ -1114,7 +1132,7 @@
         <v>131408.2720159498</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -1135,7 +1153,7 @@
         <v>134036.43745626879</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -1156,7 +1174,7 @@
         <v>136717.16620539417</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -1177,7 +1195,7 @@
         <v>139451.50952950204</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -1198,7 +1216,7 @@
         <v>142240.53972009209</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -1219,7 +1237,7 @@
         <v>145085.35051449394</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -1240,7 +1258,7 @@
         <v>147987.05752478383</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -1261,7 +1279,7 @@
         <v>150946.79867527951</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -1282,7 +1300,7 @@
         <v>153965.73464878512</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -1303,7 +1321,7 @@
         <v>157045.04934176081</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -1324,7 +1342,7 @@
         <v>160185.95032859602</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -1339,6 +1357,670 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6898F7DF-2892-9A4C-9DF9-7873D8ACB482}">
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" cm="1">
+        <f t="array" ref="A2:A36">_xlfn.SEQUENCE(Profile!$B$5-Profile!$B$4, 1, Profile!$B$4 + 1)</f>
+        <v>61</v>
+      </c>
+      <c r="B2" cm="1">
+        <f t="array" ref="B2:B36">_xlfn.SEQUENCE(Profile!$B$5-Profile!$B$4, 1, Profile!$B$2 + (Profile!$B$4-Profile!$B$3) + 1)</f>
+        <v>2059</v>
+      </c>
+      <c r="C2">
+        <v>150000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>62</v>
+      </c>
+      <c r="B3">
+        <v>2060</v>
+      </c>
+      <c r="C3">
+        <f>C2*1.02</f>
+        <v>153000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>63</v>
+      </c>
+      <c r="B4">
+        <v>2061</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C36" si="0">C3*1.02</f>
+        <v>156060</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>2062</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>159181.20000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>65</v>
+      </c>
+      <c r="B6">
+        <v>2063</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>162364.82400000002</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>66</v>
+      </c>
+      <c r="B7">
+        <v>2064</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>165612.12048000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>67</v>
+      </c>
+      <c r="B8">
+        <v>2065</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>168924.36288960002</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>68</v>
+      </c>
+      <c r="B9">
+        <v>2066</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>172302.85014739202</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>2067</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>175748.90715033986</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>70</v>
+      </c>
+      <c r="B11">
+        <v>2068</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>179263.88529334666</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>71</v>
+      </c>
+      <c r="B12">
+        <v>2069</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>182849.16299921359</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>72</v>
+      </c>
+      <c r="B13">
+        <v>2070</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>186506.14625919785</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>73</v>
+      </c>
+      <c r="B14">
+        <v>2071</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>190236.26918438182</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>74</v>
+      </c>
+      <c r="B15">
+        <v>2072</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>194040.99456806947</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>75</v>
+      </c>
+      <c r="B16">
+        <v>2073</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>197921.81445943087</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>76</v>
+      </c>
+      <c r="B17">
+        <v>2074</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>201880.2507486195</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>77</v>
+      </c>
+      <c r="B18">
+        <v>2075</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>205917.85576359188</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>78</v>
+      </c>
+      <c r="B19">
+        <v>2076</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>210036.21287886373</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>79</v>
+      </c>
+      <c r="B20">
+        <v>2077</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>214236.937136441</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>80</v>
+      </c>
+      <c r="B21">
+        <v>2078</v>
+      </c>
+      <c r="C21">
+        <f>C20*1.02</f>
+        <v>218521.67587916984</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>81</v>
+      </c>
+      <c r="B22">
+        <v>2079</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>222892.10939675325</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>82</v>
+      </c>
+      <c r="B23">
+        <v>2080</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="0"/>
+        <v>227349.95158468833</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>83</v>
+      </c>
+      <c r="B24">
+        <v>2081</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>231896.95061638209</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>84</v>
+      </c>
+      <c r="B25">
+        <v>2082</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>236534.88962870973</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>85</v>
+      </c>
+      <c r="B26">
+        <v>2083</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>241265.58742128394</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>86</v>
+      </c>
+      <c r="B27">
+        <v>2084</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>246090.89916970962</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>87</v>
+      </c>
+      <c r="B28">
+        <v>2085</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>251012.71715310382</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>88</v>
+      </c>
+      <c r="B29">
+        <v>2086</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>256032.9714961659</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>89</v>
+      </c>
+      <c r="B30">
+        <v>2087</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>261153.63092608922</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>90</v>
+      </c>
+      <c r="B31">
+        <v>2088</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>266376.70354461099</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>91</v>
+      </c>
+      <c r="B32">
+        <v>2089</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>271704.2376155032</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>92</v>
+      </c>
+      <c r="B33">
+        <v>2090</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>277138.32236781326</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>93</v>
+      </c>
+      <c r="B34">
+        <v>2091</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>282681.08881516953</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>94</v>
+      </c>
+      <c r="B35">
+        <v>2092</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>288334.71059147292</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>95</v>
+      </c>
+      <c r="B36">
+        <v>2093</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>294101.40480330237</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1603,7 +2285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1640,7 +2322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/templates/contribution_template.xlsx
+++ b/templates/contribution_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Tristan/Documents/GitHub-repos/401-k-Modeller/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DFE79-28C8-F44B-9DAD-5ECEB1199683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8748C354-BD4E-3D41-8F8C-232FF87B5FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="33">
   <si>
     <t>Field</t>
   </si>
@@ -152,10 +152,13 @@
     <t>End Age</t>
   </si>
   <si>
-    <t>Withdrawl ($)</t>
-  </si>
-  <si>
     <t>Traditional Bracket Limit (%)</t>
+  </si>
+  <si>
+    <t>Target Net Take-Home ($)</t>
+  </si>
+  <si>
+    <t>Take-Home Income ($)</t>
   </si>
 </sst>
 </file>
@@ -619,19 +622,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -642,22 +646,25 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" cm="1">
         <f t="array" ref="A2:A34">_xlfn.SEQUENCE(Profile!$B$4-Profile!$B$3+1, 1, Profile!$B$3)</f>
         <v>28</v>
@@ -670,16 +677,19 @@
         <v>85000</v>
       </c>
       <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>57828.5</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>29</v>
       </c>
@@ -691,16 +701,19 @@
         <v>86700</v>
       </c>
       <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>58883.35</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>30</v>
       </c>
@@ -712,16 +725,19 @@
         <v>88434</v>
       </c>
       <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>59959.296999999897</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>31</v>
       </c>
@@ -733,16 +749,19 @@
         <v>90202.680000000008</v>
       </c>
       <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>64114.990740000001</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>32</v>
       </c>
@@ -754,16 +773,19 @@
         <v>92006.733600000007</v>
       </c>
       <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>65387.750554799997</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>33</v>
       </c>
@@ -775,16 +797,19 @@
         <v>93846.868272000007</v>
       </c>
       <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>66685.965565895996</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>34</v>
       </c>
@@ -796,16 +821,19 @@
         <v>95723.805637440004</v>
       </c>
       <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="H8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>68010.144877213897</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>35</v>
       </c>
@@ -817,16 +845,19 @@
         <v>97638.281750188806</v>
       </c>
       <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>69360.807774758199</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>36</v>
       </c>
@@ -838,16 +869,19 @@
         <v>99591.047385192578</v>
       </c>
       <c r="D10">
-        <v>15</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>70738.483930253293</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>37</v>
       </c>
@@ -859,16 +893,19 @@
         <v>101582.86833289643</v>
       </c>
       <c r="D11">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>72143.713608858394</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>38</v>
       </c>
@@ -880,16 +917,19 @@
         <v>103614.52569955436</v>
       </c>
       <c r="D12">
-        <v>15</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>73577.0478810356</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>39</v>
       </c>
@@ -901,16 +941,19 @@
         <v>105686.81621354545</v>
       </c>
       <c r="D13">
-        <v>15</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>75039.048838656294</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>40</v>
       </c>
@@ -922,16 +965,19 @@
         <v>107800.55253781636</v>
       </c>
       <c r="D14">
-        <v>15</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>76530.289815429394</v>
+      </c>
+      <c r="E14">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>41</v>
       </c>
@@ -943,16 +989,19 @@
         <v>109956.56358857268</v>
       </c>
       <c r="D15">
-        <v>15</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>78051.355611738007</v>
+      </c>
+      <c r="E15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>42</v>
       </c>
@@ -964,16 +1013,19 @@
         <v>112155.69486034414</v>
       </c>
       <c r="D16">
-        <v>15</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="H16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>79602.842723972703</v>
+      </c>
+      <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>43</v>
       </c>
@@ -985,16 +1037,19 @@
         <v>114398.80875755103</v>
       </c>
       <c r="D17">
-        <v>15</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-      <c r="H17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>81156.460834060403</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>44</v>
       </c>
@@ -1006,16 +1061,19 @@
         <v>116686.78493270205</v>
       </c>
       <c r="D18">
-        <v>15</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-      <c r="H18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>82576.150050741606</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>45</v>
       </c>
@@ -1027,16 +1085,19 @@
         <v>119020.52063135609</v>
       </c>
       <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-      <c r="H19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>84024.233051756397</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>46</v>
       </c>
@@ -1048,16 +1109,19 @@
         <v>121400.93104398322</v>
       </c>
       <c r="D20">
-        <v>15</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="H20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>85501.277712791503</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>47</v>
       </c>
@@ -1069,16 +1133,19 @@
         <v>123828.94966486288</v>
       </c>
       <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-      <c r="H21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>87007.863267047403</v>
+      </c>
+      <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>48</v>
       </c>
@@ -1090,16 +1157,19 @@
         <v>126305.52865816014</v>
       </c>
       <c r="D22">
-        <v>15</v>
-      </c>
-      <c r="F22">
-        <v>5</v>
-      </c>
-      <c r="H22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>88544.580532388296</v>
+      </c>
+      <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>49</v>
       </c>
@@ -1111,16 +1181,19 @@
         <v>128831.63923132334</v>
       </c>
       <c r="D23">
-        <v>15</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="H23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>90112.032143036093</v>
+      </c>
+      <c r="E23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>50</v>
       </c>
@@ -1132,16 +1205,19 @@
         <v>131408.2720159498</v>
       </c>
       <c r="D24">
-        <v>15</v>
-      </c>
-      <c r="F24">
-        <v>5</v>
-      </c>
-      <c r="H24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+        <v>91710.832785896797</v>
+      </c>
+      <c r="E24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>51</v>
       </c>
@@ -1153,16 +1229,19 @@
         <v>134036.43745626879</v>
       </c>
       <c r="D25">
-        <v>15</v>
-      </c>
-      <c r="F25">
-        <v>5</v>
-      </c>
-      <c r="H25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>93341.609441614695</v>
+      </c>
+      <c r="E25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>52</v>
       </c>
@@ -1174,16 +1253,19 @@
         <v>136717.16620539417</v>
       </c>
       <c r="D26">
-        <v>15</v>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="H26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+        <v>95005.001630447005</v>
+      </c>
+      <c r="E26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>53</v>
       </c>
@@ -1195,16 +1277,19 @@
         <v>139451.50952950204</v>
       </c>
       <c r="D27">
-        <v>15</v>
-      </c>
-      <c r="F27">
-        <v>5</v>
-      </c>
-      <c r="H27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+        <v>96701.661663056002</v>
+      </c>
+      <c r="E27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>54</v>
       </c>
@@ -1216,16 +1301,19 @@
         <v>142240.53972009209</v>
       </c>
       <c r="D28">
-        <v>15</v>
-      </c>
-      <c r="F28">
-        <v>5</v>
-      </c>
-      <c r="H28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+        <v>98432.254896317099</v>
+      </c>
+      <c r="E28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>55</v>
       </c>
@@ -1237,16 +1325,19 @@
         <v>145085.35051449394</v>
       </c>
       <c r="D29">
-        <v>15</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="H29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+        <v>100197.45999424301</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>56</v>
       </c>
@@ -1258,16 +1349,19 @@
         <v>147987.05752478383</v>
       </c>
       <c r="D30">
-        <v>15</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="H30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+        <v>101997.969194128</v>
+      </c>
+      <c r="E30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>57</v>
       </c>
@@ -1279,16 +1373,19 @@
         <v>150946.79867527951</v>
       </c>
       <c r="D31">
-        <v>15</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="H31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>103834.48857801</v>
+      </c>
+      <c r="E31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>58</v>
       </c>
@@ -1300,16 +1397,19 @@
         <v>153965.73464878512</v>
       </c>
       <c r="D32">
-        <v>15</v>
-      </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
-      <c r="H32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+        <v>105707.73834957099</v>
+      </c>
+      <c r="E32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>59</v>
       </c>
@@ -1321,16 +1421,19 @@
         <v>157045.04934176081</v>
       </c>
       <c r="D33">
-        <v>15</v>
-      </c>
-      <c r="F33">
-        <v>5</v>
-      </c>
-      <c r="H33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+        <v>107618.453116562</v>
+      </c>
+      <c r="E33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>60</v>
       </c>
@@ -1342,12 +1445,15 @@
         <v>160185.95032859602</v>
       </c>
       <c r="D34">
-        <v>15</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
-      <c r="H34" t="s">
+        <v>109567.38217889301</v>
+      </c>
+      <c r="E34">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1375,13 +1481,13 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
